--- a/data/trans_orig/IP07A05-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP07A05-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse satisfecho con su vida en 2007 (tasa de respuesta: 99,7%)</t>
+          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida, percibida por el adulto en 2007 (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>691</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5702</t>
+          <t>5703</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>699</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6004</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2658</t>
+          <t>2407</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10079</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11661</t>
+          <t>11660</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18610</t>
+          <t>18706</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15973</t>
+          <t>15367</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24321</t>
+          <t>24304</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29528</t>
+          <t>29702</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40406</t>
+          <t>41004</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>77,24%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1976</t>
+          <t>1820</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8003</t>
+          <t>7958</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3582</t>
+          <t>3483</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11451</t>
+          <t>11520</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7449</t>
+          <t>7415</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16631</t>
+          <t>17147</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>32,3%</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3060</t>
+          <t>4439</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>3110</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16774</t>
+          <t>17062</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27159</t>
+          <t>27469</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24153</t>
+          <t>23597</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36018</t>
+          <t>36173</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44558</t>
+          <t>43972</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61042</t>
+          <t>59326</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>58,47%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12782</t>
+          <t>13313</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23599</t>
+          <t>23607</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>15496</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27249</t>
+          <t>27206</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>31770</t>
+          <t>32474</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>47261</t>
+          <t>47682</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,99%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1222</t>
+          <t>1208</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6925</t>
+          <t>6834</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1205</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6821</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3117</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10923</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>655</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5843</t>
+          <t>5858</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>653</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6503</t>
+          <t>5950</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3172</t>
+          <t>3166</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3167</t>
+          <t>2888</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12410</t>
+          <t>12408</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22196</t>
+          <t>21563</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>61,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8006</t>
+          <t>7839</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15964</t>
+          <t>16002</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22655</t>
+          <t>22338</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34637</t>
+          <t>35226</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>53,84%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10754</t>
+          <t>11437</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20495</t>
+          <t>20732</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11152</t>
+          <t>11792</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19772</t>
+          <t>20370</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26089</t>
+          <t>25277</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>38588</t>
+          <t>38150</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>58,31%</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4725</t>
+          <t>4739</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>633</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5714</t>
+          <t>5744</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1437</t>
+          <t>1456</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8388</t>
+          <t>8217</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3492</t>
+          <t>3457</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3821</t>
+          <t>3462</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6311</t>
+          <t>6226</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15264</t>
+          <t>15233</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8815</t>
+          <t>8932</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18716</t>
+          <t>18316</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17224</t>
+          <t>17196</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30755</t>
+          <t>30443</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,18%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>18119</t>
+          <t>18168</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>27839</t>
+          <t>28000</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>16981</t>
+          <t>16449</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>27358</t>
+          <t>26879</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>37491</t>
+          <t>38547</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>52353</t>
+          <t>52736</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,88%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2590</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10706</t>
+          <t>9820</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>1182</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6560</t>
+          <t>7385</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5543</t>
+          <t>4916</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>15152</t>
+          <t>14260</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>18,35%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5408</t>
+          <t>5411</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12435</t>
+          <t>12796</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7224</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>15482</t>
+          <t>14918</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>14498</t>
+          <t>14810</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>25621</t>
+          <t>25765</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,78%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5522</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12490</t>
+          <t>12800</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5639</t>
+          <t>6261</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>13477</t>
+          <t>14102</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>13456</t>
+          <t>13426</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>24527</t>
+          <t>24396</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>57,55%</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3249</t>
+          <t>3351</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4306</t>
+          <t>4567</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>637</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5368</t>
+          <t>5497</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4213</t>
+          <t>4138</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>4703</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>7279</t>
+          <t>7292</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>15466</t>
+          <t>15257</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>8770</t>
+          <t>8248</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>17007</t>
+          <t>16528</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>17573</t>
+          <t>16874</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>29395</t>
+          <t>28772</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>49,52%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>10433</t>
+          <t>10639</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>18821</t>
+          <t>18705</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>11250</t>
+          <t>11430</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>19575</t>
+          <t>20087</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>24393</t>
+          <t>24444</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>36195</t>
+          <t>36814</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>63,36%</t>
         </is>
       </c>
     </row>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4275</t>
+          <t>4039</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>657</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5672</t>
+          <t>6116</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8114</t>
+          <t>8342</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,36%</t>
         </is>
       </c>
     </row>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3466</t>
+          <t>3487</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3468</t>
+          <t>4184</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>24919</t>
+          <t>25069</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>37186</t>
+          <t>37717</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>21366</t>
+          <t>22021</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>34317</t>
+          <t>33914</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>49396</t>
+          <t>50684</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>67399</t>
+          <t>68255</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>57,32%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>15719</t>
+          <t>15454</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>27339</t>
+          <t>27462</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>22536</t>
+          <t>22715</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>35323</t>
+          <t>35213</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>41588</t>
+          <t>42174</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>59176</t>
+          <t>59623</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>50,07%</t>
         </is>
       </c>
     </row>
@@ -5055,7 +5055,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>6756</t>
+          <t>6157</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2717</t>
+          <t>2176</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>10457</t>
+          <t>10502</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>4168</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>13826</t>
+          <t>13783</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2948</t>
+          <t>3810</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>4199</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3243</t>
+          <t>3899</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3239</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>17780</t>
+          <t>17514</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>30697</t>
+          <t>29972</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>24148</t>
+          <t>24269</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>36971</t>
+          <t>36909</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>44639</t>
+          <t>44562</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>63549</t>
+          <t>63711</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,48%</t>
         </is>
       </c>
     </row>
@@ -5619,12 +5619,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>36475</t>
+          <t>36993</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>50460</t>
+          <t>50335</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5634,12 +5634,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>30153</t>
+          <t>30536</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>44014</t>
+          <t>43372</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>70786</t>
+          <t>69247</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>90541</t>
+          <t>89693</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5704,12 +5704,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>59,81%</t>
         </is>
       </c>
     </row>
@@ -5732,12 +5732,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>4267</t>
+          <t>4128</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>12499</t>
+          <t>12851</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5747,12 +5747,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2126</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>9048</t>
+          <t>9472</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>7922</t>
+          <t>8126</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>19063</t>
+          <t>18975</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,65%</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>3373</t>
+          <t>3289</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3442</t>
+          <t>2765</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>4114</t>
+          <t>4635</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>3328</t>
+          <t>2992</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3403</t>
+          <t>3424</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>4499</t>
+          <t>4481</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>111731</t>
+          <t>111968</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>140189</t>
+          <t>139968</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>125323</t>
+          <t>125772</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>154672</t>
+          <t>154830</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>246176</t>
+          <t>245938</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>286825</t>
+          <t>285827</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>42,84%</t>
         </is>
       </c>
     </row>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>147848</t>
+          <t>146931</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>177700</t>
+          <t>177254</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6316,12 +6316,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>155550</t>
+          <t>156254</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>184939</t>
+          <t>184719</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>312933</t>
+          <t>312506</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>353106</t>
+          <t>352604</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>52,85%</t>
         </is>
       </c>
     </row>
@@ -6414,12 +6414,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>20079</t>
+          <t>20154</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>36540</t>
+          <t>36468</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>22996</t>
+          <t>23180</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>40714</t>
+          <t>41102</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6484,12 +6484,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>47586</t>
+          <t>47508</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>71228</t>
+          <t>71262</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6499,7 +6499,7 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>8314</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>7949</t>
+          <t>7746</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6597,12 +6597,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>4063</t>
+          <t>3889</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>13364</t>
+          <t>13538</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -6640,12 +6640,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>603</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>5623</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6710,12 +6710,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>648</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>6422</t>
+          <t>6470</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse satisfecho con su vida en 2012 (tasa de respuesta: 97,81%)</t>
+          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida, percibida por el adulto en 2012 (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7106,12 +7106,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6311</t>
+          <t>6408</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13908</t>
+          <t>14108</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7121,12 +7121,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9731</t>
+          <t>9676</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19520</t>
+          <t>18911</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17815</t>
+          <t>18102</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30549</t>
+          <t>30694</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>56,76%</t>
         </is>
       </c>
     </row>
@@ -7219,12 +7219,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5697</t>
+          <t>5712</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13317</t>
+          <t>13610</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7254,12 +7254,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6998</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16219</t>
+          <t>16268</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7289,12 +7289,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14531</t>
+          <t>14533</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26805</t>
+          <t>26804</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7114</t>
+          <t>6799</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1169</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6627</t>
+          <t>7126</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3685</t>
+          <t>3194</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11326</t>
+          <t>10850</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,06%</t>
         </is>
       </c>
     </row>
@@ -7450,7 +7450,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3633</t>
+          <t>4839</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7485,7 +7485,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>5428</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7500,7 +7500,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>583</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6209</t>
+          <t>6192</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -7598,7 +7598,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2565</t>
+          <t>2628</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7613,7 +7613,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3255</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -7788,12 +7788,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20006</t>
+          <t>20286</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31420</t>
+          <t>31206</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27384</t>
+          <t>26889</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38638</t>
+          <t>38274</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7838,12 +7838,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51058</t>
+          <t>50869</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66955</t>
+          <t>66856</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7873,12 +7873,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>66,74%</t>
         </is>
       </c>
     </row>
@@ -7901,12 +7901,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11127</t>
+          <t>11661</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21952</t>
+          <t>22301</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12591</t>
+          <t>12639</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23455</t>
+          <t>23396</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7951,12 +7951,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26828</t>
+          <t>26563</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>42414</t>
+          <t>42438</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7986,12 +7986,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,36%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>937</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>6913</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>671</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7140</t>
+          <t>7101</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4488</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>583</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5034</t>
+          <t>5092</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>657</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6517</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3062</t>
+          <t>3335</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8280,7 +8280,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3307</t>
+          <t>3619</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4640</t>
+          <t>4657</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -8470,12 +8470,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6622</t>
+          <t>6687</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14860</t>
+          <t>14734</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8485,12 +8485,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6755</t>
+          <t>6975</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15290</t>
+          <t>15782</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15963</t>
+          <t>15828</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27908</t>
+          <t>28369</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>50,08%</t>
         </is>
       </c>
     </row>
@@ -8583,12 +8583,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10661</t>
+          <t>10787</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18899</t>
+          <t>18834</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8598,12 +8598,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8618,12 +8618,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11072</t>
+          <t>11061</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20153</t>
+          <t>19900</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8633,12 +8633,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24071</t>
+          <t>23772</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>36473</t>
+          <t>36626</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>64,66%</t>
         </is>
       </c>
     </row>
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1284</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6830</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7180</t>
+          <t>7355</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3697</t>
+          <t>2879</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2859</t>
+          <t>3448</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -8962,7 +8962,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3283</t>
+          <t>3306</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8977,7 +8977,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8997,7 +8997,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3277</t>
+          <t>3258</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9012,7 +9012,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -9152,12 +9152,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9124</t>
+          <t>9195</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19016</t>
+          <t>18620</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9187,12 +9187,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10842</t>
+          <t>10381</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20683</t>
+          <t>20173</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9202,12 +9202,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>22266</t>
+          <t>22273</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36045</t>
+          <t>36596</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9237,12 +9237,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>50,15%</t>
         </is>
       </c>
     </row>
@@ -9265,12 +9265,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13944</t>
+          <t>14023</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>24236</t>
+          <t>24322</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9280,12 +9280,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>63,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9300,12 +9300,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9412</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>18917</t>
+          <t>18972</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9315,12 +9315,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9335,12 +9335,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>25610</t>
+          <t>26169</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>39778</t>
+          <t>40554</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9350,12 +9350,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>55,58%</t>
         </is>
       </c>
     </row>
@@ -9378,12 +9378,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2393</t>
+          <t>2475</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10713</t>
+          <t>10483</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9393,12 +9393,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9413,12 +9413,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>1610</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7455</t>
+          <t>8033</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5372</t>
+          <t>5290</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>15031</t>
+          <t>14723</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
@@ -9644,7 +9644,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4433</t>
+          <t>4048</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9659,7 +9659,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9679,7 +9679,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4203</t>
+          <t>4755</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -9834,12 +9834,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>2419</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9530</t>
+          <t>9189</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9869,12 +9869,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>773</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6065</t>
+          <t>6186</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4274</t>
+          <t>4298</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>12993</t>
+          <t>13210</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>32,4%</t>
         </is>
       </c>
     </row>
@@ -9947,12 +9947,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9690</t>
+          <t>9662</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>17008</t>
+          <t>16777</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9982,12 +9982,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10585</t>
+          <t>11219</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>17473</t>
+          <t>17507</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>22653</t>
+          <t>23086</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>32912</t>
+          <t>32993</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,93%</t>
         </is>
       </c>
     </row>
@@ -10065,7 +10065,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4960</t>
+          <t>5158</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10080,7 +10080,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>640</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>4693</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7533</t>
+          <t>8447</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>20,72%</t>
         </is>
       </c>
     </row>
@@ -10326,7 +10326,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4387</t>
+          <t>3553</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -10361,7 +10361,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3478</t>
+          <t>3717</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>9,12%</t>
         </is>
       </c>
     </row>
@@ -10516,12 +10516,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2161</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>9225</t>
+          <t>8639</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10531,12 +10531,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3049</t>
+          <t>3065</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>10581</t>
+          <t>10631</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>6678</t>
+          <t>6755</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>16661</t>
+          <t>16347</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>28,82%</t>
         </is>
       </c>
     </row>
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>14489</t>
+          <t>14233</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>23216</t>
+          <t>22706</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10644,12 +10644,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10664,12 +10664,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>14509</t>
+          <t>14314</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>22151</t>
+          <t>22016</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10699,12 +10699,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>30813</t>
+          <t>31351</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>43052</t>
+          <t>43287</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>76,32%</t>
         </is>
       </c>
     </row>
@@ -10742,12 +10742,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>2213</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>8971</t>
+          <t>9044</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10757,12 +10757,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2203</t>
+          <t>2170</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>9895</t>
+          <t>9887</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,43%</t>
         </is>
       </c>
     </row>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3038</t>
+          <t>3777</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10875,7 +10875,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10930,7 +10930,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>4278</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -10973,7 +10973,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>4874</t>
+          <t>6599</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -11008,7 +11008,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4274</t>
+          <t>4466</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -11023,7 +11023,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -11038,12 +11038,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>682</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6732</t>
+          <t>7444</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -11053,12 +11053,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>11649</t>
+          <t>11596</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>22935</t>
+          <t>23476</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11213,12 +11213,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11233,12 +11233,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>13178</t>
+          <t>13974</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>25291</t>
+          <t>24995</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11268,12 +11268,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>27584</t>
+          <t>27509</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>43514</t>
+          <t>43464</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>38,81%</t>
         </is>
       </c>
     </row>
@@ -11311,12 +11311,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>30651</t>
+          <t>29722</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>42530</t>
+          <t>41856</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11326,12 +11326,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>25434</t>
+          <t>26876</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>38228</t>
+          <t>38158</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11381,12 +11381,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>60262</t>
+          <t>60895</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>76693</t>
+          <t>77728</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11396,12 +11396,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>69,4%</t>
         </is>
       </c>
     </row>
@@ -11424,12 +11424,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>662</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>6262</t>
+          <t>6767</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11459,12 +11459,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>1866</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>8451</t>
+          <t>8253</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11474,12 +11474,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11494,12 +11494,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>3461</t>
+          <t>3521</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>11915</t>
+          <t>11639</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11509,12 +11509,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -11542,7 +11542,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3635</t>
+          <t>3898</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11557,7 +11557,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3744</t>
+          <t>3380</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11627,7 +11627,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -11880,12 +11880,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>19155</t>
+          <t>19074</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>32078</t>
+          <t>32207</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11895,12 +11895,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11915,12 +11915,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>15975</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>29723</t>
+          <t>29312</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11930,12 +11930,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11950,12 +11950,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>38855</t>
+          <t>39417</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>58429</t>
+          <t>58085</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11965,12 +11965,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,5%</t>
         </is>
       </c>
     </row>
@@ -11993,12 +11993,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>40221</t>
+          <t>40026</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>54737</t>
+          <t>54295</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12008,47 +12008,47 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
+          <t>50,28%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>68,2%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>46900</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>40185</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>53947</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>58,97%</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
           <t>50,52%</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>68,76%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>46900</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>39786</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>53886</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>58,97%</t>
-        </is>
-      </c>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>50,02%</t>
-        </is>
-      </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>84364</t>
+          <t>85023</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>104745</t>
+          <t>104799</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12078,12 +12078,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>65,85%</t>
         </is>
       </c>
     </row>
@@ -12106,12 +12106,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>2499</t>
+          <t>2440</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>9962</t>
+          <t>9770</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t>4955</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>13528</t>
+          <t>13732</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>8909</t>
+          <t>8633</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>20769</t>
+          <t>20159</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12191,12 +12191,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -12224,7 +12224,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>3027</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12239,7 +12239,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12259,7 +12259,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>4579</t>
+          <t>4735</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12289,12 +12289,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>580</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>5231</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12304,12 +12304,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -12337,7 +12337,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2929</t>
+          <t>3214</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12352,7 +12352,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -12407,7 +12407,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>3820</t>
+          <t>2915</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -12562,12 +12562,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>99302</t>
+          <t>98295</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>127265</t>
+          <t>126384</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12597,12 +12597,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>110246</t>
+          <t>110034</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>139237</t>
+          <t>139856</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12612,12 +12612,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12632,12 +12632,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>217769</t>
+          <t>218049</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>258594</t>
+          <t>258627</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12647,12 +12647,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,64%</t>
         </is>
       </c>
     </row>
@@ -12675,12 +12675,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>162906</t>
+          <t>162873</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>192042</t>
+          <t>192118</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12710,12 +12710,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>154927</t>
+          <t>155316</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>186082</t>
+          <t>185221</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12725,12 +12725,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12745,12 +12745,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>325838</t>
+          <t>326822</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>367315</t>
+          <t>367572</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12760,12 +12760,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>56,33%</t>
         </is>
       </c>
     </row>
@@ -12788,12 +12788,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>18603</t>
+          <t>18022</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>34875</t>
+          <t>34540</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12823,12 +12823,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>19191</t>
+          <t>18688</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>33553</t>
+          <t>34212</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12838,12 +12838,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12858,12 +12858,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>39747</t>
+          <t>39093</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>62300</t>
+          <t>61998</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,5%</t>
         </is>
       </c>
     </row>
@@ -12901,12 +12901,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>7940</t>
+          <t>7946</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12916,7 +12916,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>2541</t>
+          <t>2414</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>11227</t>
+          <t>10078</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12951,12 +12951,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12971,12 +12971,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>4739</t>
+          <t>4663</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>14999</t>
+          <t>15370</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12986,12 +12986,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -13014,12 +13014,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>624</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>7463</t>
+          <t>7651</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13049,12 +13049,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>10296</t>
+          <t>9887</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13064,12 +13064,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13084,12 +13084,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>3934</t>
+          <t>3908</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>14282</t>
+          <t>14261</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13285,7 +13285,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse satisfecho con su vida en 2016 (tasa de respuesta: 98,62%)</t>
+          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida, percibida por el adulto en 2016 (tasa de respuesta: 98,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4218</t>
+          <t>4174</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11728</t>
+          <t>11975</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13495,12 +13495,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13515,12 +13515,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4935</t>
+          <t>5189</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13327</t>
+          <t>13492</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13530,12 +13530,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13550,12 +13550,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11472</t>
+          <t>11772</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22348</t>
+          <t>23538</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13565,12 +13565,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>41,14%</t>
         </is>
       </c>
     </row>
@@ -13593,12 +13593,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10902</t>
+          <t>10271</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19586</t>
+          <t>19311</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13608,12 +13608,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13628,12 +13628,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9898</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18825</t>
+          <t>18843</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13663,12 +13663,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23696</t>
+          <t>23157</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36078</t>
+          <t>35408</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13678,12 +13678,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>61,88%</t>
         </is>
       </c>
     </row>
@@ -13706,12 +13706,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2964</t>
+          <t>3012</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9929</t>
+          <t>10930</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13721,12 +13721,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13741,12 +13741,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>716</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6617</t>
+          <t>6298</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13756,12 +13756,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4988</t>
+          <t>4984</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13958</t>
+          <t>14105</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,65%</t>
         </is>
       </c>
     </row>
@@ -13859,7 +13859,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5155</t>
+          <t>4892</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5479</t>
+          <t>4852</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -13909,7 +13909,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -13937,7 +13937,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3321</t>
+          <t>3191</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3249</t>
+          <t>3176</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14022,7 +14022,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -14162,12 +14162,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20689</t>
+          <t>20882</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32400</t>
+          <t>32638</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14177,12 +14177,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14197,12 +14197,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25399</t>
+          <t>24680</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37488</t>
+          <t>38150</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14212,12 +14212,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14232,12 +14232,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48986</t>
+          <t>49671</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66932</t>
+          <t>66460</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14247,12 +14247,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>60,37%</t>
         </is>
       </c>
     </row>
@@ -14275,12 +14275,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16011</t>
+          <t>16453</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27793</t>
+          <t>27901</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14290,12 +14290,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14310,12 +14310,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18150</t>
+          <t>17992</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30682</t>
+          <t>30760</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14325,12 +14325,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14345,12 +14345,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>37661</t>
+          <t>38164</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>55229</t>
+          <t>54515</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14360,12 +14360,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>49,52%</t>
         </is>
       </c>
     </row>
@@ -14388,12 +14388,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1343</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8779</t>
+          <t>8283</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14403,12 +14403,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14428,7 +14428,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3327</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14443,7 +14443,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>1682</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9826</t>
+          <t>10144</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14473,12 +14473,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -14654,7 +14654,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4159</t>
+          <t>4730</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14669,7 +14669,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14689,7 +14689,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4756</t>
+          <t>5061</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14704,7 +14704,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11483</t>
+          <t>11620</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21621</t>
+          <t>21966</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -14859,12 +14859,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -14879,12 +14879,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12749</t>
+          <t>12409</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22044</t>
+          <t>22509</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -14894,12 +14894,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14914,12 +14914,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26818</t>
+          <t>27301</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41117</t>
+          <t>41285</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -14929,12 +14929,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>59,92%</t>
         </is>
       </c>
     </row>
@@ -14957,12 +14957,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12893</t>
+          <t>12419</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23251</t>
+          <t>22919</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -14972,12 +14972,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -14992,12 +14992,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8571</t>
+          <t>8252</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17956</t>
+          <t>17629</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15007,12 +15007,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15027,12 +15027,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23258</t>
+          <t>23506</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37431</t>
+          <t>37492</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15042,12 +15042,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>54,42%</t>
         </is>
       </c>
     </row>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15105,12 +15105,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>711</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6575</t>
+          <t>6568</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15120,12 +15120,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15140,12 +15140,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1639</t>
+          <t>1723</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9265</t>
+          <t>8653</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15155,12 +15155,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -15526,12 +15526,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19331</t>
+          <t>19413</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29719</t>
+          <t>29742</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15541,12 +15541,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15561,12 +15561,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21253</t>
+          <t>21220</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32460</t>
+          <t>32776</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15576,12 +15576,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15596,12 +15596,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>43931</t>
+          <t>44161</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>58825</t>
+          <t>59410</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15611,12 +15611,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>71,37%</t>
         </is>
       </c>
     </row>
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8752</t>
+          <t>8463</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18574</t>
+          <t>17926</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15654,12 +15654,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -15674,12 +15674,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>7559</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>19248</t>
+          <t>18433</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15689,12 +15689,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -15709,12 +15709,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>18857</t>
+          <t>18940</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>33636</t>
+          <t>34103</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -15724,12 +15724,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,97%</t>
         </is>
       </c>
     </row>
@@ -15757,7 +15757,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4943</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -15772,7 +15772,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -15787,12 +15787,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1366</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7896</t>
+          <t>7251</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -15802,12 +15802,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -15822,12 +15822,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2165</t>
+          <t>2132</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9809</t>
+          <t>9526</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -15837,12 +15837,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,44%</t>
         </is>
       </c>
     </row>
@@ -15870,7 +15870,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3699</t>
+          <t>3002</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -15885,7 +15885,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -15940,7 +15940,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3108</t>
+          <t>3531</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15955,7 +15955,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -16208,12 +16208,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>1377</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7887</t>
+          <t>7704</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16223,12 +16223,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16243,12 +16243,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10293</t>
+          <t>10640</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16258,12 +16258,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16278,12 +16278,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6016</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>14944</t>
+          <t>15135</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16293,12 +16293,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>33,36%</t>
         </is>
       </c>
     </row>
@@ -16321,12 +16321,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8714</t>
+          <t>8614</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>15974</t>
+          <t>16327</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16336,12 +16336,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>13419</t>
+          <t>12995</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>21183</t>
+          <t>21117</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16371,12 +16371,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16391,12 +16391,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>25472</t>
+          <t>25027</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>35860</t>
+          <t>34803</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16406,12 +16406,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>76,72%</t>
         </is>
       </c>
     </row>
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>662</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5960</t>
+          <t>6375</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16449,12 +16449,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16469,12 +16469,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>591</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5177</t>
+          <t>5127</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16484,12 +16484,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>8508</t>
+          <t>8803</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16519,12 +16519,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>19,4%</t>
         </is>
       </c>
     </row>
@@ -16552,7 +16552,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3358</t>
+          <t>3539</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -16567,7 +16567,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -16622,7 +16622,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>4405</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -16637,7 +16637,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>9,71%</t>
         </is>
       </c>
     </row>
@@ -16890,12 +16890,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>17157</t>
+          <t>17259</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>25772</t>
+          <t>25806</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -16905,12 +16905,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16925,12 +16925,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>16414</t>
+          <t>17277</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>25644</t>
+          <t>25707</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -16940,12 +16940,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>37066</t>
+          <t>37722</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>48711</t>
+          <t>49294</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -16975,12 +16975,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>80,28%</t>
         </is>
       </c>
     </row>
@@ -17003,12 +17003,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>3503</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>10365</t>
+          <t>10978</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -17018,12 +17018,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -17038,12 +17038,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3126</t>
+          <t>3151</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>11257</t>
+          <t>11303</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -17053,12 +17053,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>8340</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>19371</t>
+          <t>18391</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -17088,12 +17088,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>29,95%</t>
         </is>
       </c>
     </row>
@@ -17121,7 +17121,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5181</t>
+          <t>4526</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17136,7 +17136,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17156,7 +17156,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5076</t>
+          <t>5493</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>791</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>7056</t>
+          <t>7600</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17201,12 +17201,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>12,38%</t>
         </is>
       </c>
     </row>
@@ -17234,7 +17234,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>4134</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17249,7 +17249,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17269,7 +17269,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17284,7 +17284,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6385</t>
+          <t>6243</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17319,7 +17319,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,17%</t>
         </is>
       </c>
     </row>
@@ -17572,12 +17572,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>19707</t>
+          <t>19061</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>32479</t>
+          <t>32177</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -17587,12 +17587,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -17607,12 +17607,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>20640</t>
+          <t>20690</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>34240</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -17622,12 +17622,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>43438</t>
+          <t>43456</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>61438</t>
+          <t>61308</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -17657,12 +17657,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>46,35%</t>
         </is>
       </c>
     </row>
@@ -17685,12 +17685,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>28773</t>
+          <t>29626</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>42158</t>
+          <t>42426</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -17700,12 +17700,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -17720,12 +17720,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>28227</t>
+          <t>27874</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>41033</t>
+          <t>41657</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -17735,12 +17735,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -17755,12 +17755,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>61911</t>
+          <t>62090</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>80723</t>
+          <t>80503</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -17770,12 +17770,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>60,87%</t>
         </is>
       </c>
     </row>
@@ -17798,12 +17798,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1403</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>7986</t>
+          <t>8144</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -17813,12 +17813,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -17838,7 +17838,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>4349</t>
+          <t>4284</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -17853,7 +17853,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -17868,12 +17868,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2556</t>
+          <t>2572</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>9936</t>
+          <t>10281</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -17883,12 +17883,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -17916,7 +17916,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>4468</t>
+          <t>4972</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -17931,7 +17931,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -17951,7 +17951,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>5237</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -17966,7 +17966,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -17986,7 +17986,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>7406</t>
+          <t>6843</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -18001,7 +18001,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -18029,7 +18029,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3845</t>
+          <t>3884</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -18044,7 +18044,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -18099,7 +18099,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>4378</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -18114,7 +18114,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -18254,12 +18254,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>23063</t>
+          <t>23321</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>37454</t>
+          <t>36291</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -18269,12 +18269,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -18289,12 +18289,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>24799</t>
+          <t>24611</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>38617</t>
+          <t>39003</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -18304,12 +18304,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -18324,12 +18324,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>52220</t>
+          <t>52792</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>71921</t>
+          <t>72425</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -18339,12 +18339,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>46,14%</t>
         </is>
       </c>
     </row>
@@ -18367,12 +18367,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>35982</t>
+          <t>35854</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>50535</t>
+          <t>50381</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -18382,12 +18382,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -18402,12 +18402,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>34358</t>
+          <t>33971</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>48426</t>
+          <t>48854</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -18417,12 +18417,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -18437,12 +18437,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>73736</t>
+          <t>73192</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>94008</t>
+          <t>93695</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -18452,12 +18452,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>59,69%</t>
         </is>
       </c>
     </row>
@@ -18480,12 +18480,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>2823</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>10730</t>
+          <t>10913</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -18495,12 +18495,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -18515,12 +18515,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>667</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>6013</t>
+          <t>6175</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -18530,12 +18530,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -18550,12 +18550,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>4615</t>
+          <t>4545</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>14213</t>
+          <t>13837</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -18565,12 +18565,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -18593,12 +18593,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>515</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>4541</t>
+          <t>4681</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -18608,12 +18608,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -18633,7 +18633,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3677</t>
+          <t>3155</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -18648,7 +18648,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -18663,12 +18663,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>617</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>5982</t>
+          <t>5718</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -18683,7 +18683,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -18936,12 +18936,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>140380</t>
+          <t>141120</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>171105</t>
+          <t>171141</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -18951,12 +18951,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -18971,12 +18971,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>156566</t>
+          <t>155334</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>186644</t>
+          <t>187166</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -18986,12 +18986,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -19006,12 +19006,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>307394</t>
+          <t>306581</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>351236</t>
+          <t>350560</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -19021,12 +19021,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>49,0%</t>
         </is>
       </c>
     </row>
@@ -19049,12 +19049,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>150512</t>
+          <t>150258</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>183954</t>
+          <t>180635</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -19064,12 +19064,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>148297</t>
+          <t>148238</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>179901</t>
+          <t>180689</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -19099,12 +19099,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -19119,12 +19119,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>306227</t>
+          <t>307059</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>351236</t>
+          <t>351845</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>49,18%</t>
         </is>
       </c>
     </row>
@@ -19162,12 +19162,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>19973</t>
+          <t>19242</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>35538</t>
+          <t>35710</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -19177,12 +19177,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>11400</t>
+          <t>11357</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>24947</t>
+          <t>25410</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -19212,12 +19212,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -19232,12 +19232,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>34252</t>
+          <t>35039</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>55827</t>
+          <t>56341</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -19247,12 +19247,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>2547</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>10788</t>
+          <t>10864</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -19295,7 +19295,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -19310,12 +19310,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>1644</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>9475</t>
+          <t>9849</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -19330,7 +19330,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -19345,12 +19345,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>5461</t>
+          <t>5851</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>16241</t>
+          <t>17110</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -19360,12 +19360,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -19393,7 +19393,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>4252</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -19408,7 +19408,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -19428,7 +19428,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>4588</t>
+          <t>4249</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -19443,7 +19443,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -19458,12 +19458,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>656</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -19478,7 +19478,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
